--- a/stories/arbres/TREE-REL-003.xlsx
+++ b/stories/arbres/TREE-REL-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, puis au petit parc d'à côté. Un camarade a bousculé Lina, par accident. Lina recule. Maman est déjà au banc du parc. Papa viendra plus tard. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Près du ballon rouge, un camarade a bousculé. Voici le ballon rouge. La couverture est toute douce. Lina s'approche, sans courir. Papa n'est pas loin. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade a bousculé. Que fait-on ? Avec le ballon rouge.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2223,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2392,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Tom, après le ballon rouge. Un gravier roule sous une semelle. Tom reste à sa place. Lina aussi. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2583,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2750,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le ballon rouge et Tom. La tasse est encore tiède. On dit merci. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le ballon rouge et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le ballon rouge et Tom. Une abeille bourdonne loin. On attend un petit moment. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3614,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi Léa, après le ballon rouge. Une vague chuchote. Lina touche Léa tout doucement. Maman dit : je suis là. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+          <t>Lina a choisi Léa, après le ballon rouge. Une vague chuchote. Lina touche Léa tout doucement. Je suis là. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3752,13 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Léa, après le ballon rouge. Une vague chuchote. Lina touche Léa tout doucement.
+maman|Je suis là.
+narrateur|Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4112,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le ballon rouge et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse le matin à sa place. Lina est près de maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4279,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4446,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le ballon rouge et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse après la sieste à sa place. Lina est près de maman. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4613,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4780,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le ballon rouge et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse le soir à sa place. Lina est près de maman. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4947,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5114,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Sami, après le ballon rouge. Un coq chante une fois. Sami est là. Lina pose les mains à vue, loin de l'autre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5305,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5472,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le ballon rouge et Sami. Un pigeon roucoule. On essuie une miette. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5639,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5806,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le ballon rouge et Sami. La cuillère tinte. On referme un livre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5973,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6140,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le ballon rouge et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6307,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6474,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Près du seau bleu, un camarade a bousculé. Lina s'occupe du seau bleu. Un papillon passe sans bruit. Maman sourit. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6655,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade a bousculé. Que fait-on ? Avec le seau bleu.</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6828,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6837,6 +7021,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7190,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Tom, après le seau bleu. Le seau sonne, tout léger. Lina choisit Tom. Papa n'est pas loin. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le seau bleu et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse le matin à sa place. Lina est près de maman. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le seau bleu et Tom. Le banc est tiède. On se tait une seconde. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse après la sieste à sa place. Lina est près de maman. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le seau bleu et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Léa, après le seau bleu. Ça sent le savon des mains. Léa est là. Lina pose les mains à vue, loin de l'autre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le seau bleu et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le seau bleu et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le seau bleu et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Sami, après le seau bleu. Le bois de la table est lisse. Près de Sami, Lina prend le temps. Pas de course. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10130,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin, après le seau bleu et Sami. Une plume vole. On range les chaussures. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Maman dit : je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
+          <t>Lina rejoint le matin, après le seau bleu et Sami. Une plume vole. On range les chaussures. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10268,13 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le seau bleu et Sami. Une plume vole. On range les chaussures. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10437,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10175,7 +10466,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste, après le seau bleu et Sami. Le pain croustille. On met le doudou près de soi. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Maman dit : je t'ai entendu. Papa aussi. On se serre un peu.</t>
+          <t>Lina rejoint après la sieste, après le seau bleu et Sami. Le pain croustille. On met le doudou près de soi. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10313,6 +10604,12 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le seau bleu et Sami. Le pain croustille. On met le doudou près de soi. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.
+maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10772,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10499,7 +10801,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir, après le seau bleu et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Maman dit : je t'ai entendu. Papa aussi. On rentre.</t>
+          <t>Lina rejoint le soir, après le seau bleu et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Je t'ai entendu. Papa aussi. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10637,6 +10939,12 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le seau bleu et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.
+maman|Je t'ai entendu. Papa aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11107,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11274,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Près du doudou, un camarade a bousculé. Voilà le doudou. L'eau fait un tout petit bruit. Lina pose les pieds par terre, près de maman. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11455,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade a bousculé. Que fait-on ? Avec le doudou.</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11628,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11493,6 +11821,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11657,6 +11990,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Tom, après le doudou. Ça sent l'herbe coupée. Près de Tom, Lina prend le temps. Pas de course. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12181,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12348,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le doudou et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina quitte ce moment et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12515,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12682,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le doudou et Tom. Le train souffle au loin. On pose le sac. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12849,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13016,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le doudou et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina nomme encore le mot, tout bas. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13183,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13350,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Léa, après le doudou. Le bois de la table est lisse. Lina montre Léa à maman. Elle nomme ce qu'elle sent. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13541,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13708,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le doudou et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina quitte ce moment et va vers maman. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13875,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14042,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le doudou et Léa. Le bois de la table est lisse. On attend la réponse. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14209,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14376,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le doudou et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina nomme encore le mot, tout bas. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14543,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14710,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi Sami, après le doudou. Un gravier roule sous une semelle. On parle de Sami. Lina écoute jusqu'au bout. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14901,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15068,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin, après le doudou et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina range le matin un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15235,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15402,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste, après le doudou et Sami. La clochette de la porte tinte. On dit stop, tout clair. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15569,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15736,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir, après le doudou et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15903,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15957,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-003.xlsx
+++ b/stories/arbres/TREE-REL-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|À l'école, puis au petit parc d'à côté. Un camarade a bousculé Lina, par accident. Lina recule. Maman est déjà au banc du parc. Papa viendra plus tard. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1692,11 @@
           <t>narrateur|Près du ballon rouge, un camarade a bousculé. Voici le ballon rouge. La couverture est toute douce. Lina s'approche, sans courir. Papa n'est pas loin. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1880,7 @@
           <t>narrateur|Un camarade a bousculé. Que fait-on ? Avec le ballon rouge.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2052,11 @@
           <t>narrateur|Oui. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2252,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2420,11 @@
           <t>narrateur|Lina a choisi Tom, après le ballon rouge. Un gravier roule sous une semelle. Tom reste à sa place. Lina aussi. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2616,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2784,11 @@
           <t>narrateur|Lina rejoint le matin, après le ballon rouge et Tom. La tasse est encore tiède. On dit merci. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3124,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le ballon rouge et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3464,11 @@
           <t>narrateur|Lina rejoint le soir, après le ballon rouge et Tom. Une abeille bourdonne loin. On attend un petit moment. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3806,11 @@
 narrateur|Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +4002,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4170,11 @@
           <t>narrateur|Lina rejoint le matin, après le ballon rouge et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse le matin à sa place. Lina est près de maman. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4510,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le ballon rouge et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse après la sieste à sa place. Lina est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4850,11 @@
           <t>narrateur|Lina rejoint le soir, après le ballon rouge et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse le soir à sa place. Lina est près de maman. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +5022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5190,11 @@
           <t>narrateur|Lina a choisi Sami, après le ballon rouge. Un coq chante une fois. Sami est là. Lina pose les mains à vue, loin de l'autre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5310,6 +5386,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5477,6 +5554,11 @@
           <t>narrateur|Lina rejoint le matin, après le ballon rouge et Sami. Un pigeon roucoule. On essuie une miette. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5726,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5894,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le ballon rouge et Sami. La cuillère tinte. On referme un livre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6066,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6145,6 +6234,11 @@
           <t>narrateur|Lina rejoint le soir, après le ballon rouge et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6312,6 +6406,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6574,11 @@
           <t>narrateur|Près du seau bleu, un camarade a bousculé. Lina s'occupe du seau bleu. Un papillon passe sans bruit. Maman sourit. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6662,6 +6762,7 @@
           <t>narrateur|Un camarade a bousculé. Que fait-on ? Avec le seau bleu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6833,6 +6934,11 @@
           <t>narrateur|Oui. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7134,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7302,11 @@
           <t>narrateur|Lina a choisi Tom, après le seau bleu. Le seau sonne, tout léger. Lina choisit Tom. Papa n'est pas loin. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7498,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7666,11 @@
           <t>narrateur|Lina rejoint le matin, après le seau bleu et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse le matin à sa place. Lina est près de maman. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7838,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +8006,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le seau bleu et Tom. Le banc est tiède. On se tait une seconde. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. On laisse après la sieste à sa place. Lina est près de maman. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8178,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8346,11 @@
           <t>narrateur|Lina rejoint le soir, après le seau bleu et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8518,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8686,11 @@
           <t>narrateur|Lina a choisi Léa, après le seau bleu. Ça sent le savon des mains. Léa est là. Lina pose les mains à vue, loin de l'autre. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8882,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +9050,11 @@
           <t>narrateur|Lina rejoint le matin, après le seau bleu et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9222,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9390,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le seau bleu et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9562,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9730,11 @@
           <t>narrateur|Lina rejoint le soir, après le seau bleu et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9902,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +10070,11 @@
           <t>narrateur|Lina a choisi Sami, après le seau bleu. Le bois de la table est lisse. Près de Sami, Lina prend le temps. Pas de course. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10266,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10275,6 +10436,11 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10442,6 +10608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10610,6 +10777,11 @@
 maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10777,6 +10949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10945,6 +11118,11 @@
 maman|Je t'ai entendu. Papa aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11112,6 +11290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11279,6 +11458,11 @@
           <t>narrateur|Près du doudou, un camarade a bousculé. Voilà le doudou. L'eau fait un tout petit bruit. Lina pose les pieds par terre, près de maman. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11462,6 +11646,7 @@
           <t>narrateur|Un camarade a bousculé. Que fait-on ? Avec le doudou.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11633,6 +11818,11 @@
           <t>narrateur|Oui. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11828,6 +12018,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11995,6 +12186,11 @@
           <t>narrateur|Lina a choisi Tom, après le doudou. Ça sent l'herbe coupée. Près de Tom, Lina prend le temps. Pas de course. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12186,6 +12382,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12353,6 +12550,11 @@
           <t>narrateur|Lina rejoint le matin, après le doudou et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina quitte ce moment et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12520,6 +12722,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12687,6 +12890,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le doudou et Tom. Le train souffle au loin. On pose le sac. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12854,6 +13062,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13021,6 +13230,11 @@
           <t>narrateur|Lina rejoint le soir, après le doudou et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina nomme encore le mot, tout bas. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13188,6 +13402,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13355,6 +13570,11 @@
           <t>narrateur|Lina a choisi Léa, après le doudou. Le bois de la table est lisse. Lina montre Léa à maman. Elle nomme ce qu'elle sent. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13546,6 +13766,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13713,6 +13934,11 @@
           <t>narrateur|Lina rejoint le matin, après le doudou et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina quitte ce moment et va vers maman. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13880,6 +14106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14047,6 +14274,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le doudou et Léa. Le bois de la table est lisse. On attend la réponse. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina serre la main de maman, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14214,6 +14446,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14381,6 +14614,11 @@
           <t>narrateur|Lina rejoint le soir, après le doudou et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina nomme encore le mot, tout bas. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14548,6 +14786,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14715,6 +14954,11 @@
           <t>narrateur|Lina a choisi Sami, après le doudou. Un gravier roule sous une semelle. On parle de Sami. Lina écoute jusqu'au bout. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14906,6 +15150,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15073,6 +15318,11 @@
           <t>narrateur|Lina rejoint le matin, après le doudou et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina range le matin un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15240,6 +15490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15407,6 +15658,11 @@
           <t>narrateur|Lina rejoint après la sieste, après le doudou et Sami. La clochette de la porte tinte. On dit stop, tout clair. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15574,6 +15830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15741,6 +15998,11 @@
           <t>narrateur|Lina rejoint le soir, après le doudou et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Lina dit stop. Elle s'éloigne. Elle va vers papa ou maman, le parent au parc, au banc. Lina dit merci à maman. Papa sourit. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15908,6 +16170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15926,7 +16189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15964,6 +16227,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15978,7 +16255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16165,6 +16442,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
